--- a/MiniTemplate/Datas/home.xlsx
+++ b/MiniTemplate/Datas/home.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6305F6B2-5D2E-46EE-B597-1FE423F52D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6131FB-E68A-40AC-9BD9-929D512F87BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="155">
   <si>
     <t>##var</t>
   </si>
@@ -617,6 +617,22 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeStoreScale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具店下的缩放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sprite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图集路径</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -952,15 +968,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I73"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="6" max="6" width="39.5546875" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" customWidth="1"/>
+    <col min="6" max="6" width="39.5" customWidth="1"/>
+    <col min="7" max="7" width="20.75" customWidth="1"/>
+    <col min="8" max="8" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -982,8 +999,14 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1005,8 +1028,14 @@
       <c r="G2" s="1" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1028,8 +1057,14 @@
       <c r="G3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1051,8 +1086,14 @@
       <c r="G4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -1068,8 +1109,11 @@
       <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1085,8 +1129,11 @@
       <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>2000</v>
       </c>
@@ -1102,8 +1149,11 @@
       <c r="F7" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>2001</v>
       </c>
@@ -1122,8 +1172,11 @@
       <c r="G8" s="1">
         <v>2000</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>2002</v>
       </c>
@@ -1142,8 +1195,11 @@
       <c r="G9" s="1">
         <v>2000</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" s="1">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>2003</v>
       </c>
@@ -1159,8 +1215,11 @@
       <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" s="1">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>2004</v>
       </c>
@@ -1176,8 +1235,11 @@
       <c r="F11" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="1">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>2005</v>
       </c>
@@ -1193,8 +1255,11 @@
       <c r="F12" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" s="1">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>2006</v>
       </c>
@@ -1210,8 +1275,11 @@
       <c r="F13" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>2007</v>
       </c>
@@ -1227,8 +1295,11 @@
       <c r="F14" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" s="1">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>2008</v>
       </c>
@@ -1247,8 +1318,11 @@
       <c r="G15" s="1">
         <v>2007</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" s="1">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>2009</v>
       </c>
@@ -1264,8 +1338,11 @@
       <c r="F16" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>3000</v>
       </c>
@@ -1281,8 +1358,11 @@
       <c r="F17" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H17" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>3001</v>
       </c>
@@ -1298,8 +1378,11 @@
       <c r="F18" s="1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H18" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>3002</v>
       </c>
@@ -1315,8 +1398,11 @@
       <c r="F19" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="1">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>3003</v>
       </c>
@@ -1332,8 +1418,11 @@
       <c r="F20" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="1">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>3004</v>
       </c>
@@ -1353,7 +1442,7 @@
         <v>3003</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>3005</v>
       </c>
@@ -1370,7 +1459,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>3006</v>
       </c>
@@ -1387,7 +1476,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>3007</v>
       </c>
@@ -1404,7 +1493,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>3008</v>
       </c>
@@ -1421,7 +1510,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>4000</v>
       </c>
@@ -1438,7 +1527,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>4001</v>
       </c>
@@ -1455,7 +1544,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>4002</v>
       </c>
@@ -1472,7 +1561,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>4003</v>
       </c>
@@ -1492,7 +1581,7 @@
         <v>4002</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>4004</v>
       </c>
@@ -1509,7 +1598,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>4005</v>
       </c>
@@ -1526,7 +1615,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>5000</v>
       </c>
@@ -1543,7 +1632,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33">
         <v>5001</v>
       </c>
@@ -1560,7 +1649,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>5002</v>
       </c>
@@ -1578,7 +1667,7 @@
       </c>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35">
         <v>5003</v>
       </c>
@@ -1595,7 +1684,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B36">
         <v>5004</v>
       </c>
@@ -1612,7 +1701,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>5005</v>
       </c>
@@ -1629,7 +1718,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>5006</v>
       </c>
@@ -1646,7 +1735,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>5007</v>
       </c>
@@ -1663,7 +1752,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>5008</v>
       </c>
@@ -1680,7 +1769,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41">
         <v>5009</v>
       </c>
@@ -1697,7 +1786,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42">
         <v>5010</v>
       </c>
@@ -1714,7 +1803,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43">
         <v>5011</v>
       </c>
@@ -1731,7 +1820,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>6000</v>
       </c>
@@ -1748,7 +1837,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B45">
         <v>6001</v>
       </c>
@@ -1765,7 +1854,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46">
         <v>6002</v>
       </c>
@@ -1782,7 +1871,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B47">
         <v>6003</v>
       </c>
@@ -1802,7 +1891,7 @@
         <v>6002</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48">
         <v>6004</v>
       </c>
@@ -1819,7 +1908,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B49">
         <v>6005</v>
       </c>
@@ -1836,7 +1925,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B50">
         <v>6006</v>
       </c>
@@ -1853,7 +1942,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51">
         <v>6007</v>
       </c>
@@ -1870,7 +1959,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52">
         <v>6008</v>
       </c>
@@ -1887,7 +1976,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53">
         <v>7000</v>
       </c>
@@ -1904,7 +1993,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54">
         <v>7001</v>
       </c>
@@ -1921,7 +2010,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55">
         <v>7002</v>
       </c>
@@ -1938,7 +2027,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B56">
         <v>7003</v>
       </c>
@@ -1955,7 +2044,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B57">
         <v>7004</v>
       </c>
@@ -1972,7 +2061,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B58">
         <v>7005</v>
       </c>
@@ -1989,7 +2078,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B59">
         <v>7006</v>
       </c>
@@ -2006,7 +2095,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60">
         <v>7007</v>
       </c>
@@ -2023,7 +2112,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61">
         <v>8000</v>
       </c>
@@ -2040,7 +2129,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62">
         <v>8001</v>
       </c>
@@ -2057,7 +2146,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B63">
         <v>8002</v>
       </c>
@@ -2074,7 +2163,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B64">
         <v>8003</v>
       </c>
@@ -2091,7 +2180,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B65">
         <v>8004</v>
       </c>
@@ -2108,7 +2197,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B66">
         <v>8005</v>
       </c>
@@ -2125,7 +2214,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B67">
         <v>8006</v>
       </c>
@@ -2142,7 +2231,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B68">
         <v>8007</v>
       </c>
@@ -2159,7 +2248,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B69">
         <v>8008</v>
       </c>
@@ -2176,7 +2265,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B70">
         <v>8009</v>
       </c>
@@ -2193,7 +2282,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B71">
         <v>8010</v>
       </c>
@@ -2210,7 +2299,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B72">
         <v>8011</v>
       </c>
@@ -2227,7 +2316,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B73">
         <v>8012</v>
       </c>

--- a/MiniTemplate/Datas/home.xlsx
+++ b/MiniTemplate/Datas/home.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6131FB-E68A-40AC-9BD9-929D512F87BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F996915-175C-4ED6-AC49-FD37011D9542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="222">
   <si>
     <t>##var</t>
   </si>
@@ -634,6 +634,208 @@
   <si>
     <t>图集路径</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[hallway_chair]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[hallway_box]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasGame.spriteatlasv2[game_computer_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasGame.spriteatlasv2[game_chair]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasGame.spriteatlasv2[game_light]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasGame.spriteatlasv2[game_di_tan]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasGame.spriteatlasv2[game_machine]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasGame.spriteatlasv2[game_storage_box]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasGame.spriteatlasv2[game_bed]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasGame.spriteatlasv2[game_desktop_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasGame.spriteatlasv2[game_box]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasWashroom.spriteatlasv2[washroom_di_tan]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasWashroom.spriteatlasv2[washroom_plant]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasWashroom.spriteatlasv2[washroom_toilet]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasWashroom.spriteatlasv2[washroom_bathtub]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasWashroom.spriteatlasv2[washroom_clothe_busket]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasWashroom.spriteatlasv2[washroom_desk_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasWashroom.spriteatlasv2[washroom_wash_basin]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasWashroom.spriteatlasv2[washroom_towel]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasWashroom.spriteatlasv2[washroom_desk]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasKitchen.spriteatlasv2[kitchen_fridge]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasKitchen.spriteatlasv2[kitchen_di_tan]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasKitchen.spriteatlasv2[kitchen_tableware]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasKitchen.spriteatlasv2[kitchen_table_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasKitchen.spriteatlasv2[kitchen_hearth]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasKitchen.spriteatlasv2[kitchen_wash_basin]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[living_room_di_tan_1]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[living_room_di_tan_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[living_room_sofa_1]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[living_room_light]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[living_room_little_desk]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[living_room_sofa_desk]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[living_room_storage_cabinet]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[living_room_tv]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[living_room_eat_desk_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[living_room_plant_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasLivingroom.spriteatlasv2[living_room_plant_1]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom.spriteatlasv2[bedroom_plant]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom.spriteatlasv2[bedroom_bed]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom.spriteatlasv2[bedroom_beside_table]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom.spriteatlasv2[bedroom_beside_light]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom.spriteatlasv2[bedroom_closet]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom.spriteatlasv2[bedroom_desk]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom.spriteatlasv2[bedroom_dressing_table]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom.spriteatlasv2[bedroom_light]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom.spriteatlasv2[bedroom_table]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom2.spriteatlasv2[bedroom_2_bed]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom2.spriteatlasv2[bedroom_2_beside_table]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom2.spriteatlasv2[bedroom_2_beside_light]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom2.spriteatlasv2[bedroom_2_closet]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom2.spriteatlasv2[bedroom_2_sofa]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom2.spriteatlasv2[bedroom_2_storage_box]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom2.spriteatlasv2[bedroom_2_storage_box_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBedroom2.spriteatlasv2[bedroom_2_desk]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_di_tan]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_kettle]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_plant_1]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_plant_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_plant_3]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_plant_4]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_clothe_hanger_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_clothe_hanger_1]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_storage_box]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_desk_left]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_cane_chair]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_sofa]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Home/SpriteAtlasBalcony.spriteatlasv2[balcony_desk]</t>
   </si>
 </sst>
 </file>
@@ -969,15 +1171,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I73"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="6" max="6" width="39.5" customWidth="1"/>
-    <col min="7" max="7" width="20.75" customWidth="1"/>
-    <col min="8" max="8" width="19.25" customWidth="1"/>
+    <col min="6" max="6" width="39.44140625" customWidth="1"/>
+    <col min="7" max="7" width="20.77734375" customWidth="1"/>
+    <col min="8" max="8" width="19.21875" customWidth="1"/>
+    <col min="9" max="9" width="80.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1006,7 +1209,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1035,7 +1238,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1064,7 +1267,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1093,7 +1296,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -1112,8 +1315,11 @@
       <c r="H5">
         <v>4000</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I5" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1132,8 +1338,11 @@
       <c r="H6">
         <v>4000</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>2000</v>
       </c>
@@ -1152,8 +1361,11 @@
       <c r="H7">
         <v>3000</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>2001</v>
       </c>
@@ -1175,8 +1387,11 @@
       <c r="H8" s="1">
         <v>4000</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>2002</v>
       </c>
@@ -1198,8 +1413,11 @@
       <c r="H9" s="1">
         <v>3500</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>2003</v>
       </c>
@@ -1218,8 +1436,11 @@
       <c r="H10" s="1">
         <v>2500</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>2004</v>
       </c>
@@ -1238,8 +1459,11 @@
       <c r="H11" s="1">
         <v>3500</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>2005</v>
       </c>
@@ -1258,8 +1482,11 @@
       <c r="H12" s="1">
         <v>3500</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I12" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>2006</v>
       </c>
@@ -1278,8 +1505,11 @@
       <c r="H13" s="1">
         <v>4000</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>2007</v>
       </c>
@@ -1298,8 +1528,11 @@
       <c r="H14" s="1">
         <v>2500</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>2008</v>
       </c>
@@ -1321,8 +1554,11 @@
       <c r="H15" s="1">
         <v>3500</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>2009</v>
       </c>
@@ -1341,8 +1577,11 @@
       <c r="H16" s="1">
         <v>5000</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="I16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>3000</v>
       </c>
@@ -1361,8 +1600,11 @@
       <c r="H17" s="1">
         <v>3000</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="I17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>3001</v>
       </c>
@@ -1381,8 +1623,11 @@
       <c r="H18" s="1">
         <v>3000</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="I18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>3002</v>
       </c>
@@ -1401,8 +1646,11 @@
       <c r="H19" s="1">
         <v>2500</v>
       </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="I19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>3003</v>
       </c>
@@ -1421,8 +1669,11 @@
       <c r="H20" s="1">
         <v>2300</v>
       </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="I20" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>3004</v>
       </c>
@@ -1441,8 +1692,14 @@
       <c r="G21" s="1">
         <v>3003</v>
       </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H21" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I21" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>3005</v>
       </c>
@@ -1458,8 +1715,14 @@
       <c r="F22" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H22">
+        <v>3000</v>
+      </c>
+      <c r="I22" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>3006</v>
       </c>
@@ -1475,8 +1738,14 @@
       <c r="F23" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H23">
+        <v>3000</v>
+      </c>
+      <c r="I23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>3007</v>
       </c>
@@ -1492,8 +1761,14 @@
       <c r="F24" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H24">
+        <v>3000</v>
+      </c>
+      <c r="I24" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>3008</v>
       </c>
@@ -1509,8 +1784,14 @@
       <c r="F25" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H25">
+        <v>3000</v>
+      </c>
+      <c r="I25" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>4000</v>
       </c>
@@ -1526,8 +1807,14 @@
       <c r="F26" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H26">
+        <v>2500</v>
+      </c>
+      <c r="I26" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>4001</v>
       </c>
@@ -1543,8 +1830,14 @@
       <c r="F27" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H27">
+        <v>3500</v>
+      </c>
+      <c r="I27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>4002</v>
       </c>
@@ -1560,8 +1853,14 @@
       <c r="F28" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H28">
+        <v>3000</v>
+      </c>
+      <c r="I28" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>4003</v>
       </c>
@@ -1580,8 +1879,14 @@
       <c r="G29" s="1">
         <v>4002</v>
       </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H29">
+        <v>4000</v>
+      </c>
+      <c r="I29" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>4004</v>
       </c>
@@ -1597,8 +1902,14 @@
       <c r="F30" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H30">
+        <v>3000</v>
+      </c>
+      <c r="I30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>4005</v>
       </c>
@@ -1614,8 +1925,14 @@
       <c r="F31" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H31">
+        <v>2800</v>
+      </c>
+      <c r="I31" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>5000</v>
       </c>
@@ -1631,8 +1948,14 @@
       <c r="F32" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H32">
+        <v>2800</v>
+      </c>
+      <c r="I32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>5001</v>
       </c>
@@ -1648,8 +1971,14 @@
       <c r="F33" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H33">
+        <v>4000</v>
+      </c>
+      <c r="I33" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>5002</v>
       </c>
@@ -1666,8 +1995,14 @@
         <v>67</v>
       </c>
       <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H34">
+        <v>2100</v>
+      </c>
+      <c r="I34" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>5003</v>
       </c>
@@ -1683,8 +2018,14 @@
       <c r="F35" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H35">
+        <v>4000</v>
+      </c>
+      <c r="I35" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36">
         <v>5004</v>
       </c>
@@ -1700,8 +2041,14 @@
       <c r="F36" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H36">
+        <v>5000</v>
+      </c>
+      <c r="I36" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>5005</v>
       </c>
@@ -1717,8 +2064,14 @@
       <c r="F37" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H37">
+        <v>4000</v>
+      </c>
+      <c r="I37" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>5006</v>
       </c>
@@ -1734,8 +2087,14 @@
       <c r="F38" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H38">
+        <v>4000</v>
+      </c>
+      <c r="I38" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39">
         <v>5007</v>
       </c>
@@ -1751,8 +2110,14 @@
       <c r="F39" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H39">
+        <v>3500</v>
+      </c>
+      <c r="I39" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40">
         <v>5008</v>
       </c>
@@ -1768,8 +2133,14 @@
       <c r="F40" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H40">
+        <v>4000</v>
+      </c>
+      <c r="I40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41">
         <v>5009</v>
       </c>
@@ -1785,8 +2156,14 @@
       <c r="F41" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H41">
+        <v>3500</v>
+      </c>
+      <c r="I41" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>5010</v>
       </c>
@@ -1802,8 +2179,14 @@
       <c r="F42" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H42">
+        <v>5000</v>
+      </c>
+      <c r="I42" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>5011</v>
       </c>
@@ -1819,8 +2202,14 @@
       <c r="F43" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H43">
+        <v>3800</v>
+      </c>
+      <c r="I43" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44">
         <v>6000</v>
       </c>
@@ -1836,8 +2225,14 @@
       <c r="F44" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H44">
+        <v>3800</v>
+      </c>
+      <c r="I44" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45">
         <v>6001</v>
       </c>
@@ -1853,8 +2248,14 @@
       <c r="F45" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H45">
+        <v>1500</v>
+      </c>
+      <c r="I45" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B46">
         <v>6002</v>
       </c>
@@ -1870,8 +2271,14 @@
       <c r="F46" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H46">
+        <v>4000</v>
+      </c>
+      <c r="I46" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B47">
         <v>6003</v>
       </c>
@@ -1890,8 +2297,14 @@
       <c r="G47" s="1">
         <v>6002</v>
       </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H47" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I47" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48">
         <v>6004</v>
       </c>
@@ -1907,8 +2320,14 @@
       <c r="F48" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H48" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I48" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49">
         <v>6005</v>
       </c>
@@ -1924,8 +2343,14 @@
       <c r="F49" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H49" s="1">
+        <v>3200</v>
+      </c>
+      <c r="I49" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B50">
         <v>6006</v>
       </c>
@@ -1941,8 +2366,14 @@
       <c r="F50" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H50" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I50" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51">
         <v>6007</v>
       </c>
@@ -1958,8 +2389,14 @@
       <c r="F51" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H51" s="1">
+        <v>3200</v>
+      </c>
+      <c r="I51" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52">
         <v>6008</v>
       </c>
@@ -1975,8 +2412,14 @@
       <c r="F52" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H52" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I52" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>7000</v>
       </c>
@@ -1992,8 +2435,14 @@
       <c r="F53" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H53" s="1">
+        <v>1600</v>
+      </c>
+      <c r="I53" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>7001</v>
       </c>
@@ -2009,8 +2458,14 @@
       <c r="F54" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H54" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I54" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>7002</v>
       </c>
@@ -2026,8 +2481,14 @@
       <c r="F55" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H55" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I55" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>7003</v>
       </c>
@@ -2043,8 +2504,14 @@
       <c r="F56" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H56" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I56" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57">
         <v>7004</v>
       </c>
@@ -2060,8 +2527,14 @@
       <c r="F57" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H57" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I57" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B58">
         <v>7005</v>
       </c>
@@ -2077,8 +2550,14 @@
       <c r="F58" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H58" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I58" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B59">
         <v>7006</v>
       </c>
@@ -2094,8 +2573,14 @@
       <c r="F59" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H59" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I59" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B60">
         <v>7007</v>
       </c>
@@ -2111,8 +2596,14 @@
       <c r="F60" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H60" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I60" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61">
         <v>8000</v>
       </c>
@@ -2128,8 +2619,14 @@
       <c r="F61" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H61" s="1">
+        <v>2200</v>
+      </c>
+      <c r="I61" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62">
         <v>8001</v>
       </c>
@@ -2145,8 +2642,14 @@
       <c r="F62" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H62" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I62" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63">
         <v>8002</v>
       </c>
@@ -2162,8 +2665,14 @@
       <c r="F63" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H63" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I63" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64">
         <v>8003</v>
       </c>
@@ -2179,8 +2688,14 @@
       <c r="F64" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H64" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I64" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65">
         <v>8004</v>
       </c>
@@ -2196,8 +2711,14 @@
       <c r="F65" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H65" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I65" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66">
         <v>8005</v>
       </c>
@@ -2213,8 +2734,14 @@
       <c r="F66" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H66" s="1">
+        <v>4500</v>
+      </c>
+      <c r="I66" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67">
         <v>8006</v>
       </c>
@@ -2230,8 +2757,14 @@
       <c r="F67" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H67" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I67" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>8007</v>
       </c>
@@ -2247,8 +2780,14 @@
       <c r="F68" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H68" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I68" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B69">
         <v>8008</v>
       </c>
@@ -2264,8 +2803,14 @@
       <c r="F69" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H69" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I69" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B70">
         <v>8009</v>
       </c>
@@ -2281,8 +2826,14 @@
       <c r="F70" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H70" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I70" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B71">
         <v>8010</v>
       </c>
@@ -2298,8 +2849,14 @@
       <c r="F71" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H71" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I71" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B72">
         <v>8011</v>
       </c>
@@ -2315,8 +2872,14 @@
       <c r="F72" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="H72" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I72" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B73">
         <v>8012</v>
       </c>
@@ -2331,6 +2894,12 @@
       </c>
       <c r="F73" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="H73" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I73" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/home.xlsx
+++ b/MiniTemplate/Datas/home.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F996915-175C-4ED6-AC49-FD37011D9542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B269AEB-E29B-44FF-B3A1-DE6CCB066955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1336,7 +1336,7 @@
         <v>18</v>
       </c>
       <c r="H6">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I6" t="s">
         <v>156</v>
@@ -1385,7 +1385,7 @@
         <v>2000</v>
       </c>
       <c r="H8" s="1">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I8" t="s">
         <v>158</v>
@@ -1411,7 +1411,7 @@
         <v>2000</v>
       </c>
       <c r="H9" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I9" t="s">
         <v>159</v>
@@ -1457,7 +1457,7 @@
         <v>23</v>
       </c>
       <c r="H11" s="1">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I11" t="s">
         <v>161</v>
@@ -1552,7 +1552,7 @@
         <v>2007</v>
       </c>
       <c r="H15" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I15" t="s">
         <v>159</v>
@@ -1575,7 +1575,7 @@
         <v>85</v>
       </c>
       <c r="H16" s="1">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="I16" t="s">
         <v>165</v>
@@ -1598,7 +1598,7 @@
         <v>84</v>
       </c>
       <c r="H17" s="1">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="I17" t="s">
         <v>166</v>
@@ -1621,7 +1621,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I18" t="s">
         <v>167</v>
@@ -1644,7 +1644,7 @@
         <v>82</v>
       </c>
       <c r="H19" s="1">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="I19" t="s">
         <v>168</v>
@@ -1693,7 +1693,7 @@
         <v>3003</v>
       </c>
       <c r="H21" s="1">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="I21" t="s">
         <v>171</v>
@@ -1785,7 +1785,7 @@
         <v>76</v>
       </c>
       <c r="H25">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I25" t="s">
         <v>174</v>
@@ -1831,7 +1831,7 @@
         <v>74</v>
       </c>
       <c r="H27">
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="I27" t="s">
         <v>175</v>
@@ -1854,7 +1854,7 @@
         <v>73</v>
       </c>
       <c r="H28">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="I28" t="s">
         <v>178</v>
@@ -1880,7 +1880,7 @@
         <v>4002</v>
       </c>
       <c r="H29">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I29" t="s">
         <v>177</v>
@@ -1903,7 +1903,7 @@
         <v>71</v>
       </c>
       <c r="H30">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="I30" t="s">
         <v>179</v>
@@ -1972,7 +1972,7 @@
         <v>68</v>
       </c>
       <c r="H33">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I33" t="s">
         <v>182</v>
@@ -2019,7 +2019,7 @@
         <v>66</v>
       </c>
       <c r="H35">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I35" t="s">
         <v>184</v>
@@ -2042,7 +2042,7 @@
         <v>65</v>
       </c>
       <c r="H36">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="I36" t="s">
         <v>185</v>
@@ -2088,7 +2088,7 @@
         <v>63</v>
       </c>
       <c r="H38">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I38" t="s">
         <v>187</v>
@@ -2134,7 +2134,7 @@
         <v>61</v>
       </c>
       <c r="H40">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I40" t="s">
         <v>184</v>
@@ -2203,7 +2203,7 @@
         <v>58</v>
       </c>
       <c r="H43">
-        <v>3800</v>
+        <v>3000</v>
       </c>
       <c r="I43" t="s">
         <v>191</v>
@@ -2226,7 +2226,7 @@
         <v>57</v>
       </c>
       <c r="H44">
-        <v>3800</v>
+        <v>3000</v>
       </c>
       <c r="I44" t="s">
         <v>192</v>
@@ -2249,7 +2249,7 @@
         <v>56</v>
       </c>
       <c r="H45">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I45" t="s">
         <v>193</v>
@@ -2298,7 +2298,7 @@
         <v>6002</v>
       </c>
       <c r="H47" s="1">
-        <v>4000</v>
+        <v>3200</v>
       </c>
       <c r="I47" t="s">
         <v>195</v>
@@ -2321,7 +2321,7 @@
         <v>53</v>
       </c>
       <c r="H48" s="1">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="I48" t="s">
         <v>196</v>
@@ -2367,7 +2367,7 @@
         <v>51</v>
       </c>
       <c r="H50" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I50" t="s">
         <v>198</v>
@@ -2390,7 +2390,7 @@
         <v>50</v>
       </c>
       <c r="H51" s="1">
-        <v>3200</v>
+        <v>2500</v>
       </c>
       <c r="I51" t="s">
         <v>199</v>
@@ -2436,7 +2436,7 @@
         <v>48</v>
       </c>
       <c r="H53" s="1">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="I53" t="s">
         <v>201</v>
@@ -2459,7 +2459,7 @@
         <v>47</v>
       </c>
       <c r="H54" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I54" t="s">
         <v>202</v>
@@ -2505,7 +2505,7 @@
         <v>45</v>
       </c>
       <c r="H56" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I56" t="s">
         <v>204</v>
@@ -2574,7 +2574,7 @@
         <v>42</v>
       </c>
       <c r="H59" s="1">
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="I59" t="s">
         <v>207</v>
@@ -2827,7 +2827,7 @@
         <v>31</v>
       </c>
       <c r="H70" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I70" t="s">
         <v>218</v>
